--- a/docs/DuelTank_Pin_Assignments.xlsx
+++ b/docs/DuelTank_Pin_Assignments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f61b8e6cd6058b02/Desktop/UT Stuff/Freshman Spring Classes/319H/DuelTanks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_35A82836726ABFD9C793A12B55378AB7C2473D52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D58398D3-B3CE-488D-BB61-755E3DF087FE}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="11_35A82836726ABFD9C793A12B55378AB7C2473D52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49DCAB6F-B359-47B3-B841-925148706D10}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="330">
   <si>
     <t>J1</t>
   </si>
@@ -1014,6 +1014,12 @@
   </si>
   <si>
     <t>Battle_Ready_t</t>
+  </si>
+  <si>
+    <t>StatusLED_4</t>
+  </si>
+  <si>
+    <t>StatusLED_5</t>
   </si>
 </sst>
 </file>
@@ -1398,9 +1404,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1537,6 +1540,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2115,20 +2121,22 @@
       <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:17" ht="14.5">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="83" t="s">
         <v>323</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="79" t="s">
         <v>318</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="82" t="s">
+      <c r="E5" s="81" t="s">
         <v>324</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="H5" s="9" t="s">
         <v>14</v>
       </c>
@@ -2163,7 +2171,7 @@
       <c r="K6" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="60" t="s">
+      <c r="M6" s="59" t="s">
         <v>75</v>
       </c>
       <c r="N6" s="3"/>
@@ -2172,7 +2180,7 @@
       <c r="Q6" s="3"/>
     </row>
     <row r="7" spans="1:17" ht="15.5">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="84" t="s">
         <v>322</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -2192,11 +2200,11 @@
         <v>27</v>
       </c>
       <c r="I7" s="10"/>
-      <c r="J7" s="79" t="s">
+      <c r="J7" s="78" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="3"/>
-      <c r="M7" s="60" t="s">
+      <c r="M7" s="59" t="s">
         <v>76</v>
       </c>
       <c r="N7" s="3"/>
@@ -2205,7 +2213,7 @@
       <c r="Q7" s="3"/>
     </row>
     <row r="8" spans="1:17" ht="15.5">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="84" t="s">
         <v>321</v>
       </c>
       <c r="B8" s="13" t="s">
@@ -2215,7 +2223,7 @@
       <c r="D8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="82" t="s">
+      <c r="E8" s="81" t="s">
         <v>325</v>
       </c>
       <c r="G8" s="1"/>
@@ -2229,7 +2237,7 @@
       <c r="K8" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="60" t="s">
+      <c r="M8" s="59" t="s">
         <v>77</v>
       </c>
       <c r="N8" s="3"/>
@@ -2248,7 +2256,7 @@
       <c r="D9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="82" t="s">
+      <c r="E9" s="81" t="s">
         <v>326</v>
       </c>
       <c r="G9" s="28" t="s">
@@ -2264,7 +2272,7 @@
       <c r="K9" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="60" t="s">
+      <c r="M9" s="59" t="s">
         <v>78</v>
       </c>
       <c r="N9" s="3"/>
@@ -2273,7 +2281,7 @@
       <c r="Q9" s="3"/>
     </row>
     <row r="10" spans="1:17" ht="15.5">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="84" t="s">
         <v>320</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -2283,7 +2291,7 @@
       <c r="D10" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="86" t="s">
+      <c r="E10" s="85" t="s">
         <v>327</v>
       </c>
       <c r="G10" s="28" t="s">
@@ -2299,7 +2307,7 @@
       <c r="K10" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="M10" s="60" t="s">
+      <c r="M10" s="59" t="s">
         <v>79</v>
       </c>
       <c r="N10" s="1"/>
@@ -2315,24 +2323,26 @@
         <v>47</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="81" t="s">
+      <c r="D11" s="80" t="s">
         <v>319</v>
       </c>
-      <c r="E11" s="32"/>
-      <c r="G11" s="33" t="s">
+      <c r="E11" s="86" t="s">
+        <v>328</v>
+      </c>
+      <c r="G11" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="34" t="s">
+      <c r="H11" s="33" t="s">
         <v>49</v>
       </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="35" t="s">
+      <c r="J11" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="36" t="s">
+      <c r="K11" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="M11" s="60" t="s">
+      <c r="M11" s="59" t="s">
         <v>80</v>
       </c>
       <c r="N11" s="1"/>
@@ -2344,28 +2354,28 @@
       <c r="A12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39" t="s">
+      <c r="C12" s="37"/>
+      <c r="D12" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="39" t="s">
         <v>53</v>
       </c>
       <c r="G12" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="41" t="s">
+      <c r="H12" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="38"/>
-      <c r="J12" s="42" t="s">
+      <c r="I12" s="37"/>
+      <c r="J12" s="41" t="s">
         <v>56</v>
       </c>
       <c r="K12" s="3"/>
-      <c r="M12" s="60" t="s">
+      <c r="M12" s="59" t="s">
         <v>81</v>
       </c>
       <c r="N12" s="1"/>
@@ -2388,7 +2398,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
-      <c r="M13" s="60" t="s">
+      <c r="M13" s="59" t="s">
         <v>82</v>
       </c>
       <c r="N13" s="1"/>
@@ -2397,23 +2407,23 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:17" ht="15.5">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40" t="s">
+      <c r="B14" s="42"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39" t="s">
         <v>59</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="82"/>
+      <c r="K14" s="81"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="60" t="s">
+      <c r="M14" s="59" t="s">
         <v>83</v>
       </c>
       <c r="N14" s="1"/>
@@ -2425,10 +2435,10 @@
       <c r="A15" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
       <c r="F15" s="31"/>
       <c r="G15" s="31"/>
       <c r="H15" s="31" t="s">
@@ -2447,10 +2457,10 @@
       <c r="A16" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
       <c r="F16" s="21"/>
       <c r="G16" s="21"/>
       <c r="H16" s="21" t="s">
@@ -2466,16 +2476,16 @@
       <c r="P16" s="3"/>
     </row>
     <row r="17" spans="1:16" ht="14.5">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="48" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="28"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49" t="s">
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48" t="s">
         <v>65</v>
       </c>
       <c r="I17" s="2"/>
@@ -2488,16 +2498,16 @@
       <c r="P17" s="3"/>
     </row>
     <row r="18" spans="1:16" ht="14.5">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="50" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="14"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51" t="s">
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50" t="s">
         <v>67</v>
       </c>
       <c r="I18" s="2"/>
@@ -2513,10 +2523,10 @@
       <c r="A19" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="53"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
       <c r="H19" s="17" t="s">
@@ -2532,16 +2542,16 @@
       <c r="P19" s="3"/>
     </row>
     <row r="20" spans="1:16" ht="14.5">
-      <c r="A20" s="55" t="s">
+      <c r="A20" s="54" t="s">
         <v>70</v>
       </c>
       <c r="B20" s="22"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55" t="s">
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54" t="s">
         <v>71</v>
       </c>
       <c r="I20" s="2"/>
@@ -2554,16 +2564,16 @@
       <c r="P20" s="3"/>
     </row>
     <row r="21" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="56" t="s">
         <v>72</v>
       </c>
       <c r="B21" s="6"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57" t="s">
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56" t="s">
         <v>73</v>
       </c>
       <c r="I21" s="2"/>
@@ -2576,13 +2586,13 @@
       <c r="P21" s="3"/>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="82" t="s">
         <v>74</v>
       </c>
       <c r="B22" s="26"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
       <c r="F22" s="25"/>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
@@ -2674,7 +2684,7 @@
       <c r="P32" s="3"/>
     </row>
     <row r="33" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A33" s="60"/>
+      <c r="A33" s="59"/>
       <c r="B33" s="1"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -12364,7 +12374,7 @@
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
     <row r="24" spans="3:3">
-      <c r="C24" s="61"/>
+      <c r="C24" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13502,15 +13512,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.5">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="61" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="65"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="2" spans="1:5" ht="14.5">
       <c r="A2" s="1"/>
@@ -13538,7 +13548,7 @@
     </row>
     <row r="4" spans="1:5" ht="14.5">
       <c r="A4" s="1"/>
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="65" t="s">
         <v>108</v>
       </c>
       <c r="C4" s="24" t="s">
@@ -13550,7 +13560,7 @@
     </row>
     <row r="5" spans="1:5" ht="14.5">
       <c r="A5" s="1"/>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="65" t="s">
         <v>110</v>
       </c>
       <c r="C5" s="24" t="s">
@@ -13562,7 +13572,7 @@
     </row>
     <row r="6" spans="1:5" ht="14.5">
       <c r="A6" s="1"/>
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="65" t="s">
         <v>112</v>
       </c>
       <c r="C6" s="24" t="s">
@@ -13574,7 +13584,7 @@
     </row>
     <row r="7" spans="1:5" ht="14.5">
       <c r="A7" s="1"/>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="65" t="s">
         <v>114</v>
       </c>
       <c r="C7" s="24" t="s">
@@ -13586,7 +13596,7 @@
     </row>
     <row r="8" spans="1:5" ht="14.5">
       <c r="A8" s="1"/>
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="65" t="s">
         <v>116</v>
       </c>
       <c r="C8" s="24" t="s">
@@ -13598,7 +13608,7 @@
     </row>
     <row r="9" spans="1:5" ht="14.5">
       <c r="A9" s="1"/>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="65" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="24" t="s">
@@ -13609,10 +13619,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.5">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="65" t="s">
         <v>121</v>
       </c>
       <c r="C10" s="24" t="s">
@@ -13623,10 +13633,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.5">
-      <c r="A11" s="67" t="s">
+      <c r="A11" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="65" t="s">
         <v>123</v>
       </c>
       <c r="C11" s="24" t="s">
@@ -13637,10 +13647,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.5">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="65" t="s">
         <v>125</v>
       </c>
       <c r="C12" s="24" t="s">
@@ -13651,10 +13661,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.5">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="65" t="s">
         <v>127</v>
       </c>
       <c r="C13" s="24" t="s">
@@ -13666,7 +13676,7 @@
     </row>
     <row r="14" spans="1:5" ht="14.5">
       <c r="A14" s="1"/>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="65" t="s">
         <v>129</v>
       </c>
       <c r="C14" s="24" t="s">
@@ -13678,7 +13688,7 @@
     </row>
     <row r="15" spans="1:5" ht="14.5">
       <c r="A15" s="1"/>
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="65" t="s">
         <v>131</v>
       </c>
       <c r="C15" s="24" t="s">
@@ -13690,7 +13700,7 @@
     </row>
     <row r="16" spans="1:5" ht="14.5">
       <c r="A16" s="1"/>
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="65" t="s">
         <v>133</v>
       </c>
       <c r="C16" s="24" t="s">
@@ -13702,7 +13712,7 @@
     </row>
     <row r="17" spans="1:5" ht="14.5">
       <c r="A17" s="1"/>
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="65" t="s">
         <v>135</v>
       </c>
       <c r="C17" s="24" t="s">
@@ -13714,7 +13724,7 @@
     </row>
     <row r="18" spans="1:5" ht="14.5">
       <c r="A18" s="1"/>
-      <c r="B18" s="66" t="s">
+      <c r="B18" s="65" t="s">
         <v>137</v>
       </c>
       <c r="C18" s="24" t="s">
@@ -13726,7 +13736,7 @@
     </row>
     <row r="19" spans="1:5" ht="14.5">
       <c r="A19" s="1"/>
-      <c r="B19" s="66" t="s">
+      <c r="B19" s="65" t="s">
         <v>139</v>
       </c>
       <c r="C19" s="24" t="s">
@@ -13738,7 +13748,7 @@
     </row>
     <row r="20" spans="1:5" ht="14.5">
       <c r="A20" s="1"/>
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="65" t="s">
         <v>141</v>
       </c>
       <c r="C20" s="24" t="s">
@@ -13750,7 +13760,7 @@
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="65" t="s">
         <v>143</v>
       </c>
       <c r="C21" s="24" t="s">
@@ -13764,7 +13774,7 @@
       <c r="A22" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B22" s="66" t="s">
+      <c r="B22" s="65" t="s">
         <v>146</v>
       </c>
       <c r="C22" s="24" t="s">
@@ -13776,7 +13786,7 @@
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="66" t="s">
+      <c r="B23" s="65" t="s">
         <v>148</v>
       </c>
       <c r="C23" s="24" t="s">
@@ -13788,7 +13798,7 @@
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="66" t="s">
+      <c r="B24" s="65" t="s">
         <v>150</v>
       </c>
       <c r="C24" s="24" t="s">
@@ -13800,7 +13810,7 @@
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="65" t="s">
         <v>152</v>
       </c>
       <c r="C25" s="24" t="s">
@@ -13815,17 +13825,17 @@
       <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="B27" s="63"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="68"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="67"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="66" t="s">
+      <c r="B28" s="65" t="s">
         <v>155</v>
       </c>
       <c r="C28" s="24" t="s">
@@ -13837,7 +13847,7 @@
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="66" t="s">
+      <c r="B29" s="65" t="s">
         <v>157</v>
       </c>
       <c r="C29" s="24" t="s">
@@ -13849,7 +13859,7 @@
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="66" t="s">
+      <c r="B30" s="65" t="s">
         <v>159</v>
       </c>
       <c r="C30" s="24" t="s">
@@ -13864,13 +13874,13 @@
       <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="62"/>
-      <c r="B32" s="69" t="s">
+      <c r="A32" s="61"/>
+      <c r="B32" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="63"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="68"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="67"/>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
@@ -13977,7 +13987,7 @@
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="70" t="s">
+      <c r="B42" s="69" t="s">
         <v>173</v>
       </c>
       <c r="C42" s="24" t="s">
@@ -13992,13 +14002,13 @@
       <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A44" s="62"/>
-      <c r="B44" s="69" t="s">
+      <c r="A44" s="61"/>
+      <c r="B44" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="63"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="68"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="67"/>
     </row>
     <row r="45" spans="1:5" ht="15.75" customHeight="1">
       <c r="A45" s="1"/>
@@ -14104,7 +14114,7 @@
     </row>
     <row r="54" spans="1:5" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="71" t="s">
+      <c r="B54" s="70" t="s">
         <v>184</v>
       </c>
       <c r="C54" s="24" t="s">
@@ -14119,13 +14129,13 @@
       <c r="E55" s="3"/>
     </row>
     <row r="56" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A56" s="62"/>
-      <c r="B56" s="69" t="s">
+      <c r="A56" s="61"/>
+      <c r="B56" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="68"/>
+      <c r="C56" s="62"/>
+      <c r="D56" s="62"/>
+      <c r="E56" s="67"/>
     </row>
     <row r="57" spans="1:5" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
@@ -14237,7 +14247,7 @@
     </row>
     <row r="66" spans="1:5" ht="15.75" customHeight="1">
       <c r="A66" s="1"/>
-      <c r="B66" s="70" t="s">
+      <c r="B66" s="69" t="s">
         <v>127</v>
       </c>
       <c r="C66" s="24" t="s">
@@ -14252,13 +14262,13 @@
       <c r="E67" s="3"/>
     </row>
     <row r="68" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A68" s="62"/>
-      <c r="B68" s="69" t="s">
+      <c r="A68" s="61"/>
+      <c r="B68" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="63"/>
-      <c r="D68" s="63"/>
-      <c r="E68" s="68"/>
+      <c r="C68" s="62"/>
+      <c r="D68" s="62"/>
+      <c r="E68" s="67"/>
     </row>
     <row r="69" spans="1:5" ht="15.75" customHeight="1">
       <c r="A69" s="1"/>
@@ -14364,7 +14374,7 @@
     </row>
     <row r="78" spans="1:5" ht="15.75" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="71" t="s">
+      <c r="B78" s="70" t="s">
         <v>56</v>
       </c>
       <c r="C78" s="24" t="s">
@@ -18080,7 +18090,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="11.25" customHeight="1"/>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -18097,18 +18107,18 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="73"/>
-      <c r="X2" s="73"/>
-      <c r="Y2" s="73"/>
-      <c r="Z2" s="73"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="72"/>
+      <c r="Y2" s="72"/>
+      <c r="Z2" s="72"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="71" t="s">
         <v>208</v>
       </c>
       <c r="B3" s="24" t="s">
@@ -18153,74 +18163,74 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="74"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="W3" s="73"/>
-      <c r="X3" s="73"/>
-      <c r="Y3" s="73"/>
-      <c r="Z3" s="73"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="72"/>
+      <c r="U3" s="72"/>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
+      <c r="Y3" s="72"/>
+      <c r="Z3" s="72"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="75" t="s">
         <v>220</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="75" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="76" t="s">
+      <c r="D4" s="75" t="s">
         <v>222</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="75" t="s">
         <v>223</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="75" t="s">
         <v>224</v>
       </c>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="75" t="s">
         <v>225</v>
       </c>
-      <c r="H4" s="76" t="s">
+      <c r="H4" s="75" t="s">
         <v>226</v>
       </c>
-      <c r="I4" s="76" t="s">
+      <c r="I4" s="75" t="s">
         <v>227</v>
       </c>
-      <c r="J4" s="76" t="s">
+      <c r="J4" s="75" t="s">
         <v>228</v>
       </c>
-      <c r="K4" s="76" t="s">
+      <c r="K4" s="75" t="s">
         <v>229</v>
       </c>
-      <c r="L4" s="76" t="s">
+      <c r="L4" s="75" t="s">
         <v>230</v>
       </c>
-      <c r="M4" s="76" t="s">
+      <c r="M4" s="75" t="s">
         <v>231</v>
       </c>
-      <c r="N4" s="77" t="s">
+      <c r="N4" s="76" t="s">
         <v>232</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="W4" s="73"/>
-      <c r="X4" s="73"/>
-      <c r="Y4" s="73"/>
-      <c r="Z4" s="73"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="72"/>
+      <c r="U4" s="72"/>
+      <c r="V4" s="72"/>
+      <c r="W4" s="72"/>
+      <c r="X4" s="72"/>
+      <c r="Y4" s="72"/>
+      <c r="Z4" s="72"/>
     </row>
     <row r="7" spans="1:26" ht="14.5">
-      <c r="A7" s="78"/>
+      <c r="A7" s="77"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>

--- a/docs/DuelTank_Pin_Assignments.xlsx
+++ b/docs/DuelTank_Pin_Assignments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f61b8e6cd6058b02/Desktop/UT Stuff/Freshman Spring Classes/319H/DuelTanks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="11_35A82836726ABFD9C793A12B55378AB7C2473D52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49DCAB6F-B359-47B3-B841-925148706D10}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="11_35A82836726ABFD9C793A12B55378AB7C2473D52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BF55761-5764-4515-9A2E-94C241D5CBF9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="332">
   <si>
     <t>J1</t>
   </si>
@@ -1013,13 +1013,19 @@
     <t>StatusLED_3</t>
   </si>
   <si>
-    <t>Battle_Ready_t</t>
-  </si>
-  <si>
     <t>StatusLED_4</t>
   </si>
   <si>
-    <t>StatusLED_5</t>
+    <t>Battle_Ready_t_1</t>
+  </si>
+  <si>
+    <t>Battle_Ready_t_2</t>
+  </si>
+  <si>
+    <t>LED_TX</t>
+  </si>
+  <si>
+    <t>LED_RX</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1325,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1540,9 +1546,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2118,12 +2121,12 @@
       <c r="J4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="5" spans="1:17" ht="14.5">
-      <c r="A5" s="83" t="s">
-        <v>323</v>
-      </c>
+      <c r="A5" s="83"/>
       <c r="B5" s="79" t="s">
         <v>318</v>
       </c>
@@ -2132,11 +2135,9 @@
         <v>13</v>
       </c>
       <c r="E5" s="81" t="s">
-        <v>324</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>329</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="9" t="s">
         <v>14</v>
       </c>
@@ -2144,7 +2145,9 @@
       <c r="J5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="6" spans="1:17" ht="15.5">
       <c r="A6" s="14" t="s">
@@ -2160,7 +2163,9 @@
       <c r="E6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="H6" s="9" t="s">
         <v>20</v>
       </c>
@@ -2180,9 +2185,7 @@
       <c r="Q6" s="3"/>
     </row>
     <row r="7" spans="1:17" ht="15.5">
-      <c r="A7" s="84" t="s">
-        <v>322</v>
-      </c>
+      <c r="A7" s="84"/>
       <c r="B7" s="9" t="s">
         <v>23</v>
       </c>
@@ -2213,9 +2216,7 @@
       <c r="Q7" s="3"/>
     </row>
     <row r="8" spans="1:17" ht="15.5">
-      <c r="A8" s="84" t="s">
-        <v>321</v>
-      </c>
+      <c r="A8" s="84"/>
       <c r="B8" s="13" t="s">
         <v>29</v>
       </c>
@@ -2226,7 +2227,9 @@
       <c r="E8" s="81" t="s">
         <v>325</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="81" t="s">
+        <v>327</v>
+      </c>
       <c r="H8" s="9" t="s">
         <v>31</v>
       </c>
@@ -2257,7 +2260,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="81" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>37</v>
@@ -2292,7 +2295,7 @@
         <v>42</v>
       </c>
       <c r="E10" s="85" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>43</v>
@@ -2326,8 +2329,8 @@
       <c r="D11" s="80" t="s">
         <v>319</v>
       </c>
-      <c r="E11" s="86" t="s">
-        <v>328</v>
+      <c r="E11" s="81" t="s">
+        <v>331</v>
       </c>
       <c r="G11" s="32" t="s">
         <v>48</v>
@@ -2361,8 +2364,8 @@
       <c r="D12" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="39" t="s">
-        <v>53</v>
+      <c r="E12" s="81" t="s">
+        <v>330</v>
       </c>
       <c r="G12" s="19" t="s">
         <v>54</v>
@@ -2374,7 +2377,9 @@
       <c r="J12" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="M12" s="59" t="s">
         <v>81</v>
       </c>
@@ -2390,7 +2395,9 @@
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="39" t="s">
+        <v>53</v>
+      </c>
       <c r="H13" s="24" t="s">
         <v>1</v>
       </c>
